--- a/outputs/fund_records/易方达_广发_2025_2026Q1_报会与首发记录.xlsx
+++ b/outputs/fund_records/易方达_广发_2025_2026Q1_报会与首发记录.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,10 +482,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>产品类型口径</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>与证监会基金电子披露平台（eid.csrc.gov.cn）“基金类型”下拉选项一致：股票型、货币型、债券型、混合型、QDII、短期理财债券型、基金中基金 (FOF)、商品基金、不动产投资信托基金。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>注意</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>托管人为证券公司的ETF/联接基金保留“托管人”原文；字段名写作“托管行/托管人”。</t>
         </is>
@@ -648,7 +660,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>短期理财债券型</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -707,7 +719,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -770,7 +782,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -888,7 +900,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1073,7 +1085,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>短期理财债券型</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1195,7 +1207,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1254,7 +1266,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1313,7 +1325,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1376,7 +1388,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1435,7 +1447,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1494,7 +1506,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1557,7 +1569,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1620,7 +1632,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1746,7 +1758,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1809,7 +1821,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1872,7 +1884,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1935,7 +1947,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1998,7 +2010,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2124,7 +2136,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2187,7 +2199,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2250,7 +2262,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2313,7 +2325,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2376,7 +2388,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2565,7 +2577,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2801,7 +2813,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2864,7 +2876,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2990,7 +3002,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3045,7 +3057,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3222,7 +3234,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3285,7 +3297,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3340,7 +3352,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3450,7 +3462,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3513,7 +3525,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3639,7 +3651,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3926,7 +3938,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3989,7 +4001,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4107,7 +4119,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4162,7 +4174,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4221,7 +4233,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4280,7 +4292,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4335,7 +4347,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4453,7 +4465,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4579,7 +4591,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4634,7 +4646,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>纯债/债券型</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4693,7 +4705,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4756,7 +4768,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4819,7 +4831,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4929,7 +4941,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4984,7 +4996,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5110,7 +5122,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5165,7 +5177,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5220,7 +5232,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5346,7 +5358,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5409,7 +5421,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5464,7 +5476,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5527,7 +5539,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5653,7 +5665,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5708,7 +5720,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5763,7 +5775,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5826,7 +5838,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6015,7 +6027,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6078,7 +6090,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6133,7 +6145,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6188,7 +6200,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6243,7 +6255,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6306,7 +6318,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6369,7 +6381,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6491,7 +6503,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6554,7 +6566,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6617,7 +6629,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6743,7 +6755,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6798,7 +6810,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6857,7 +6869,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7034,7 +7046,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7089,7 +7101,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7152,7 +7164,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7215,7 +7227,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7274,7 +7286,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7337,7 +7349,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7400,7 +7412,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7463,7 +7475,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7526,7 +7538,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7589,7 +7601,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7648,7 +7660,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7707,7 +7719,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7770,7 +7782,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7833,7 +7845,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7959,7 +7971,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8022,7 +8034,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8085,7 +8097,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8148,7 +8160,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8211,7 +8223,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8274,7 +8286,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8400,7 +8412,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8463,7 +8475,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8526,7 +8538,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8589,7 +8601,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8652,7 +8664,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8715,7 +8727,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8778,7 +8790,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8841,7 +8853,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8967,7 +8979,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9030,7 +9042,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9093,7 +9105,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9156,7 +9168,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9219,7 +9231,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9282,7 +9294,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9345,7 +9357,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9408,7 +9420,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9471,7 +9483,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9597,7 +9609,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9656,7 +9668,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -10089,7 +10101,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>商品基金</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10144,7 +10156,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10266,7 +10278,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10384,7 +10396,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10447,7 +10459,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10510,7 +10522,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10573,7 +10585,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>QDII</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10636,7 +10648,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10880,7 +10892,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -11061,7 +11073,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11124,7 +11136,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11187,7 +11199,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11242,7 +11254,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11305,7 +11317,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11360,7 +11372,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11423,7 +11435,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11478,7 +11490,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11541,7 +11553,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11600,7 +11612,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11655,7 +11667,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11714,7 +11726,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11773,7 +11785,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11828,7 +11840,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -12009,7 +12021,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12064,7 +12076,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12127,7 +12139,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12253,7 +12265,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12308,7 +12320,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12363,7 +12375,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12426,7 +12438,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12481,7 +12493,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12536,7 +12548,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12599,7 +12611,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12662,7 +12674,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12717,7 +12729,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12780,7 +12792,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12843,7 +12855,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12906,7 +12918,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12961,7 +12973,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -13024,7 +13036,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -13087,7 +13099,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -13150,7 +13162,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -13213,7 +13225,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13268,7 +13280,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -13386,7 +13398,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13508,7 +13520,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13571,7 +13583,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -13626,7 +13638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -13689,7 +13701,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13752,7 +13764,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -13815,7 +13827,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13937,7 +13949,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -14000,7 +14012,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>债券型/固收</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -14063,7 +14075,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -14126,7 +14138,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -14189,7 +14201,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -14244,7 +14256,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -14307,7 +14319,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -14370,7 +14382,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -14433,7 +14445,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -14496,7 +14508,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14555,7 +14567,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14618,7 +14630,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14677,7 +14689,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14736,7 +14748,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>指数型/ETF/联接</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -14964,7 +14976,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -15374,7 +15386,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -15456,7 +15468,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -15620,7 +15632,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -15784,7 +15796,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -15866,7 +15878,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -16030,7 +16042,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -16112,7 +16124,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -16194,7 +16206,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -16276,7 +16288,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -16358,7 +16370,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -16522,7 +16534,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -16604,7 +16616,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -16768,7 +16780,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -16932,7 +16944,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -17014,7 +17026,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -17178,7 +17190,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -17260,7 +17272,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -17342,7 +17354,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -17588,7 +17600,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -17670,7 +17682,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -17916,7 +17928,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -18080,7 +18092,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -18162,7 +18174,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FOF</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -18326,7 +18338,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -18408,7 +18420,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>指数型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -18572,7 +18584,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -18818,7 +18830,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -18982,7 +18994,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -19310,7 +19322,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -19966,7 +19978,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -20130,7 +20142,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>基金中基金</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -20458,7 +20470,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -21114,7 +21126,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -21442,7 +21454,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -21688,7 +21700,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -21770,7 +21782,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -22180,7 +22192,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -22508,7 +22520,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>基金中基金</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -22836,7 +22848,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -22918,7 +22930,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -23246,7 +23258,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>基金中基金</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -23820,7 +23832,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -24148,7 +24160,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -25050,7 +25062,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>基金中基金</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -25132,7 +25144,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ETF联接基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">

--- a/outputs/fund_records/易方达_广发_2025_2026Q1_报会与首发记录.xlsx
+++ b/outputs/fund_records/易方达_广发_2025_2026Q1_报会与首发记录.xlsx
@@ -6444,7 +6444,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>未识别</t>
+          <t>不动产投资信托基金</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>未识别</t>
+          <t>不动产投资信托基金</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">

--- a/outputs/fund_records/易方达_广发_2025_2026Q1_报会与首发记录.xlsx
+++ b/outputs/fund_records/易方达_广发_2025_2026Q1_报会与首发记录.xlsx
@@ -12830,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N236"/>
+  <dimension ref="A1:M236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12856,14 +12856,14 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>报会日期</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>报会日期_接收材料</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>主列表日期</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>受理通知日期</t>
@@ -12897,11 +12897,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>核验方式</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>报会日期</t>
         </is>
       </c>
     </row>
@@ -12965,11 +12960,6 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-01-03</t>
         </is>
       </c>
     </row>
@@ -13031,11 +13021,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-01-03</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13045,7 +13030,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>广发中证800指数增强型证券投资基金</t>
+          <t>广发中证智选高股息策略交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13060,7 +13045,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -13076,17 +13061,17 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>接收材料:2025-01-08; 受理通知:2025-01-10; 行政许可决定书:2025-02-17</t>
+          <t>接收材料:2025-01-08; 受理通知:2025-01-10; 行政许可决定书:2025-01-16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发中证800指数增强型证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发中证智选高股息策略交易型开放式指数证券投资基金》</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -13097,11 +13082,6 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-01-08</t>
         </is>
       </c>
     </row>
@@ -13113,7 +13093,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>广发中证智选高股息策略交易型开放式指数证券投资基金</t>
+          <t>广发中证800指数增强型证券投资基金</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13133,7 +13113,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -13144,17 +13124,17 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>接收材料:2025-01-08; 受理通知:2025-01-10; 行政许可决定书:2025-01-16</t>
+          <t>接收材料:2025-01-08; 受理通知:2025-01-10; 行政许可决定书:2025-02-17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发中证智选高股息策略交易型开放式指数证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发中证800指数增强型证券投资基金》</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -13165,11 +13145,6 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-01-07</t>
         </is>
       </c>
     </row>
@@ -13227,11 +13202,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-01-08</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13291,11 +13261,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13359,11 +13324,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13373,12 +13333,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>广发智选启航混合型证券投资基金</t>
+          <t>广发添利90天滚动持有债券型证券投资基金</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>混合型</t>
+          <t>短期理财债券型</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -13388,33 +13348,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2025-02-05</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>2025-02-12</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>接收材料:2025-02-06; 受理通知:2025-02-12; 行政许可决定书:2025-03-05</t>
+          <t>接收材料:2025-02-06; 受理通知:2025-02-12; 一次书面反馈:2025-05-12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发智选启航混合型证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发添利90天滚动持有债券型证券投资基金》</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -13425,11 +13381,6 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-02-05</t>
         </is>
       </c>
     </row>
@@ -13441,12 +13392,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>广发添利90天滚动持有债券型证券投资基金</t>
+          <t>广发资源智选股票型发起式证券投资基金</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>短期理财债券型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13456,29 +13407,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>2025-02-06</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2025-01-27</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>2025-02-12</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>接收材料:2025-02-06; 受理通知:2025-02-12; 一次书面反馈:2025-05-12</t>
+          <t>接收材料:2025-02-06; 受理通知:2025-02-12; 行政许可决定书:2025-03-19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发添利90天滚动持有债券型证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发资源智选股票型发起式证券投资基金》</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -13489,11 +13444,6 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-01-27</t>
         </is>
       </c>
     </row>
@@ -13505,12 +13455,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>广发资源智选股票型发起式证券投资基金</t>
+          <t>广发智选启航混合型证券投资基金</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>股票型</t>
+          <t>混合型</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13520,12 +13470,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13536,17 +13486,17 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>接收材料:2025-02-06; 受理通知:2025-02-12; 行政许可决定书:2025-03-19</t>
+          <t>接收材料:2025-02-06; 受理通知:2025-02-12; 行政许可决定书:2025-03-05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发资源智选股票型发起式证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发智选启航混合型证券投资基金》</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -13557,11 +13507,6 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
         </is>
       </c>
     </row>
@@ -13623,11 +13568,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-02-07</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13652,12 +13592,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2025-02-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -13687,11 +13627,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-02-11</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13753,11 +13688,6 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
         </is>
       </c>
     </row>
@@ -13819,11 +13749,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13883,11 +13808,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13951,11 +13871,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14019,11 +13934,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-03-18</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14048,12 +13958,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2025-05-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -14087,11 +13997,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14155,11 +14060,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14223,11 +14123,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14291,11 +14186,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14320,12 +14210,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -14359,11 +14249,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14427,11 +14312,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14495,11 +14375,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14563,11 +14438,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14631,11 +14501,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14699,11 +14564,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14728,12 +14588,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14767,11 +14627,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14835,11 +14690,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14903,11 +14753,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14932,12 +14777,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -14971,11 +14816,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15039,11 +14879,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15053,12 +14888,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>广发中证红利低波动指数型发起式证券投资基金</t>
+          <t>广发创新成长混合型证券投资基金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>股票型</t>
+          <t>混合型</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -15068,25 +14903,33 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>接收材料:2025-09-18</t>
+          <t>接收材料:2025-09-18; 受理通知:2025-09-22; 行政许可决定书:2025-10-23</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发中证红利低波动指数型发起式证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发创新成长混合型证券投资基金》</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -15097,11 +14940,6 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
         </is>
       </c>
     </row>
@@ -15113,12 +14951,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>广发创新成长混合型证券投资基金</t>
+          <t>广发中证红利低波动指数型发起式证券投资基金</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>混合型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -15133,28 +14971,20 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>接收材料:2025-09-18; 受理通知:2025-09-22; 行政许可决定书:2025-10-23</t>
+          <t>接收材料:2025-09-18</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发创新成长混合型证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发中证红利低波动指数型发起式证券投资基金》</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -15165,11 +14995,6 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
         </is>
       </c>
     </row>
@@ -15233,11 +15058,6 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
         </is>
       </c>
     </row>
@@ -15295,11 +15115,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15324,12 +15139,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -15363,11 +15178,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15431,11 +15241,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15499,11 +15304,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15513,7 +15313,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>广发上证科创板芯片交易型开放式指数证券投资基金</t>
+          <t>广发上证科创板芯片设计主题交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15528,7 +15328,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -15546,7 +15346,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发上证科创板芯片交易型开放式指数证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发上证科创板芯片设计主题交易型开放式指数证券投资基金》</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -15557,11 +15357,6 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15368,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>广发上证科创板芯片设计主题交易型开放式指数证券投资基金</t>
+          <t>广发上证科创板芯片交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -15593,7 +15388,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -15606,7 +15401,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发上证科创板芯片设计主题交易型开放式指数证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发上证科创板芯片交易型开放式指数证券投资基金》</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -15617,11 +15412,6 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
         </is>
       </c>
     </row>
@@ -15683,11 +15473,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15697,7 +15482,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>广发消费领航股票型发起式证券投资基金</t>
+          <t>广发国证新能源电池交易型开放式指数证券投资基金发起式联接基金</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -15717,7 +15502,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -15728,17 +15513,17 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>接收材料:2025-10-14; 受理通知:2025-10-21; 行政许可决定书:2025-11-17</t>
+          <t>接收材料:2025-10-15; 受理通知:2025-10-21; 行政许可决定书:2025-11-28</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发消费领航股票型发起式证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发国证新能源电池交易型开放式指数证券投资基金发起式联接基金》</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -15749,11 +15534,6 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
         </is>
       </c>
     </row>
@@ -15765,7 +15545,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>广发国证新能源电池交易型开放式指数证券投资基金发起式联接基金</t>
+          <t>广发消费领航股票型发起式证券投资基金</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -15780,7 +15560,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -15796,17 +15576,17 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>接收材料:2025-10-15; 受理通知:2025-10-21; 行政许可决定书:2025-11-28</t>
+          <t>接收材料:2025-10-14; 受理通知:2025-10-21; 行政许可决定书:2025-11-17</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发国证新能源电池交易型开放式指数证券投资基金发起式联接基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发消费领航股票型发起式证券投资基金》</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -15817,11 +15597,6 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
         </is>
       </c>
     </row>
@@ -15848,12 +15623,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>2025-10-20</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -15879,11 +15654,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15939,11 +15709,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -15999,11 +15764,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16067,11 +15827,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16135,11 +15890,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16164,12 +15914,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -16201,11 +15951,6 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
         </is>
       </c>
     </row>
@@ -16263,11 +16008,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16331,11 +16071,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16360,12 +16095,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -16393,11 +16128,6 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
         </is>
       </c>
     </row>
@@ -16455,11 +16185,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -16515,11 +16240,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16544,12 +16264,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -16583,11 +16303,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16612,12 +16327,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -16643,11 +16358,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16672,12 +16382,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -16709,11 +16419,6 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
         </is>
       </c>
     </row>
@@ -16771,11 +16476,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16835,11 +16535,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -16897,11 +16592,6 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
         </is>
       </c>
     </row>
@@ -16959,11 +16649,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17019,11 +16704,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17087,11 +16767,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17155,11 +16830,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17223,11 +16893,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17237,12 +16902,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>广发中证机床交易型开放式指数证券投资基金</t>
+          <t>广发稳泰多元机遇三个月持有期混合型基金中基金（ETF-FOF）</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>股票型</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -17252,25 +16917,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>接收材料:2025-12-10</t>
+          <t>接收材料:2025-12-10; 受理通知:2025-12-17; 行政许可决定书:2026-01-23</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发中证机床交易型开放式指数证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发稳泰多元机遇三个月持有期混合型基金中基金（ETF-FOF）》</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -17281,11 +16954,6 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
         </is>
       </c>
     </row>
@@ -17297,12 +16965,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>广发景旭纯债债券型证券投资基金</t>
+          <t>广发中证机床交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>债券型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -17320,21 +16988,17 @@
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>接收材料:2025-12-10; 受理通知:2025-12-17; 一次书面反馈:2026-02-06</t>
+          <t>接收材料:2025-12-10</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发景旭纯债债券型证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发中证机床交易型开放式指数证券投资基金》</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -17345,11 +17009,6 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
         </is>
       </c>
     </row>
@@ -17361,12 +17020,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>广发稳泰多元机遇三个月持有期混合型基金中基金（ETF-FOF）</t>
+          <t>广发景旭纯债债券型证券投资基金</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>基金中基金 (FOF)</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -17381,7 +17040,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -17390,19 +17049,15 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>接收材料:2025-12-10; 受理通知:2025-12-17; 行政许可决定书:2026-01-23</t>
+          <t>接收材料:2025-12-10; 受理通知:2025-12-17; 一次书面反馈:2026-02-06</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发稳泰多元机遇三个月持有期混合型基金中基金（ETF-FOF）》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发景旭纯债债券型证券投资基金》</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -17413,11 +17068,6 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
         </is>
       </c>
     </row>
@@ -17481,11 +17131,6 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
         </is>
       </c>
     </row>
@@ -17543,11 +17188,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17603,11 +17243,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -17632,12 +17267,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -17663,11 +17298,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -17692,12 +17322,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -17731,11 +17361,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -17797,11 +17422,6 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
         </is>
       </c>
     </row>
@@ -17859,11 +17479,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -17919,11 +17534,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -17933,12 +17543,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>广发招瑞多元机遇6个月持有期混合型基金中基金（FOF）</t>
+          <t>广发汇智量化选股混合型证券投资基金</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>基金中基金 (FOF)</t>
+          <t>混合型</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -17948,7 +17558,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -17964,17 +17574,17 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>接收材料:2026-01-06; 受理通知:2026-01-07; 行政许可决定书:2026-02-26</t>
+          <t>接收材料:2026-01-06; 受理通知:2026-01-07; 行政许可决定书:2026-02-10</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发招瑞多元机遇6个月持有期混合型基金中基金（FOF）》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发汇智量化选股混合型证券投资基金》</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -17985,11 +17595,6 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
         </is>
       </c>
     </row>
@@ -18001,12 +17606,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>广发汇智量化选股混合型证券投资基金</t>
+          <t>广发招瑞多元机遇6个月持有期混合型基金中基金（FOF）</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>混合型</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -18021,7 +17626,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -18032,17 +17637,17 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>接收材料:2026-01-06; 受理通知:2026-01-07; 行政许可决定书:2026-02-10</t>
+          <t>接收材料:2026-01-06; 受理通知:2026-01-07; 行政许可决定书:2026-02-26</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发汇智量化选股混合型证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发招瑞多元机遇6个月持有期混合型基金中基金（FOF）》</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -18053,11 +17658,6 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
         </is>
       </c>
     </row>
@@ -18123,11 +17723,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18152,12 +17747,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -18183,11 +17778,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18212,12 +17802,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -18251,11 +17841,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18319,11 +17904,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18348,12 +17928,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -18385,11 +17965,6 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
         </is>
       </c>
     </row>
@@ -18447,11 +18022,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18476,12 +18046,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -18507,11 +18077,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18536,12 +18101,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -18575,11 +18140,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18643,11 +18203,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18711,11 +18266,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -18725,12 +18275,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>广发稳航混合型证券投资基金</t>
+          <t>广发添享债券型证券投资基金</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>混合型</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18745,28 +18295,28 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>接收材料:2026-01-30; 受理通知:2026-02-03; 行政许可决定书:2026-04-14</t>
+          <t>接收材料:2026-02-02; 受理通知:2026-02-09; 行政许可决定书:2026-03-06</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发稳航混合型证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发添享债券型证券投资基金》</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -18777,11 +18327,6 @@
       <c r="M91" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
         </is>
       </c>
     </row>
@@ -18793,12 +18338,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>广发添享债券型证券投资基金</t>
+          <t>广发稳航混合型证券投资基金</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>债券型</t>
+          <t>混合型</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18808,7 +18353,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -18818,23 +18363,23 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>接收材料:2026-02-02; 受理通知:2026-02-09; 行政许可决定书:2026-03-06</t>
+          <t>接收材料:2026-01-30; 受理通知:2026-02-03; 行政许可决定书:2026-04-14</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发添享债券型证券投资基金》</t>
+          <t>关于广发基金管理有限公司的《公开募集基金募集申请注册-广发稳航混合型证券投资基金》</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -18845,11 +18390,6 @@
       <c r="M92" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
         </is>
       </c>
     </row>
@@ -18907,11 +18447,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18967,11 +18502,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19027,11 +18557,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19095,11 +18620,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19163,11 +18683,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19229,11 +18744,6 @@
       <c r="M98" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
         </is>
       </c>
     </row>
@@ -19295,11 +18805,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19363,11 +18868,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19431,11 +18931,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19499,11 +18994,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19565,11 +19055,6 @@
       <c r="M103" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
         </is>
       </c>
     </row>
@@ -19627,11 +19112,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19691,11 +19171,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19720,12 +19195,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -19759,11 +19234,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19788,12 +19258,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -19819,11 +19289,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -19881,11 +19346,6 @@
       <c r="M108" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -19943,11 +19403,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -20011,11 +19466,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20077,11 +19527,6 @@
       <c r="M111" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>2025-01-24</t>
         </is>
       </c>
     </row>
@@ -20143,11 +19588,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>2025-02-19</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -20211,11 +19651,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20240,12 +19675,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2025-02-25</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -20279,11 +19714,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>2025-02-25</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20347,11 +19777,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -20415,11 +19840,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20481,11 +19901,6 @@
       <c r="M117" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
         </is>
       </c>
     </row>
@@ -20547,11 +19962,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20611,11 +20021,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20679,11 +20084,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20747,11 +20147,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>2025-03-18</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -20815,11 +20210,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20883,11 +20273,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20951,11 +20336,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -21019,11 +20399,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21087,11 +20462,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21155,11 +20525,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -21223,11 +20588,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21291,11 +20651,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21359,11 +20714,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21427,11 +20777,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21495,11 +20840,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21563,11 +20903,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21631,11 +20966,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21699,11 +21029,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21767,11 +21092,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -21835,11 +21155,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21903,11 +21218,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21971,11 +21281,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -22039,11 +21344,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -22107,11 +21407,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -22175,11 +21470,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>2025-07-17</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -22204,12 +21494,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -22243,11 +21533,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -22311,11 +21596,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -22325,12 +21605,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>易方达如意盈享6个月持有期混合型发起式基金中基金（FOF）</t>
+          <t>易方达恒生生物科技交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>基金中基金 (FOF)</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -22340,7 +21620,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -22356,17 +21636,17 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>接收材料:2025-07-29; 受理通知:2025-07-30; 一次书面反馈:2025-08-11; 接收书面回复:2025-10-14; 行政许可决定书:2025-10-15</t>
+          <t>接收材料:2025-07-29; 受理通知:2025-07-30; 行政许可决定书:2025-08-06</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达如意盈享6个月持有期混合型发起式基金中基金（FOF）》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达恒生生物科技交易型开放式指数证券投资基金》</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -22377,11 +21657,6 @@
       <c r="M145" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
         </is>
       </c>
     </row>
@@ -22393,12 +21668,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>易方达恒生生物科技交易型开放式指数证券投资基金</t>
+          <t>易方达如意盈享6个月持有期混合型发起式基金中基金（FOF）</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>股票型</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -22413,7 +21688,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -22424,17 +21699,17 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>接收材料:2025-07-29; 受理通知:2025-07-30; 行政许可决定书:2025-08-06</t>
+          <t>接收材料:2025-07-29; 受理通知:2025-07-30; 一次书面反馈:2025-08-11; 接收书面回复:2025-10-14; 行政许可决定书:2025-10-15</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达恒生生物科技交易型开放式指数证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达如意盈享6个月持有期混合型发起式基金中基金（FOF）》</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -22445,11 +21720,6 @@
       <c r="M146" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
         </is>
       </c>
     </row>
@@ -22515,11 +21785,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -22583,11 +21848,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -22649,11 +21909,6 @@
       <c r="M149" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
         </is>
       </c>
     </row>
@@ -22715,11 +21970,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -22783,11 +22033,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -22851,11 +22096,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -22917,11 +22157,6 @@
       <c r="M153" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
         </is>
       </c>
     </row>
@@ -22979,11 +22214,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -23047,11 +22277,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -23115,11 +22340,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -23129,12 +22349,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>易方达科技先锋混合型证券投资基金</t>
+          <t>易方达中证沪深港黄金产业股票交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>混合型</t>
+          <t>商品基金</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -23144,33 +22364,25 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2025-10-20</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>接收材料:2025-09-09; 受理通知:2025-09-16; 行政许可决定书:2025-10-20</t>
+          <t>接收材料:2025-09-11</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达科技先锋混合型证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证沪深港黄金产业股票交易型开放式指数证券投资基金》</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -23181,11 +22393,6 @@
       <c r="M157" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
         </is>
       </c>
     </row>
@@ -23197,12 +22404,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>易方达中证沪深港黄金产业股票交易型开放式指数证券投资基金</t>
+          <t>易方达中证金融科技主题交易型开放式指数证券投资基金联接基金</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>商品基金</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -23217,20 +22424,28 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>接收材料:2025-09-11</t>
+          <t>接收材料:2025-09-11; 受理通知:2025-09-16; 一次书面反馈:2026-02-06; 接收书面回复:2026-03-23; 行政许可决定书:2026-03-23</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证沪深港黄金产业股票交易型开放式指数证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证金融科技主题交易型开放式指数证券投资基金联接基金》</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -23241,11 +22456,6 @@
       <c r="M158" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
         </is>
       </c>
     </row>
@@ -23257,12 +22467,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>易方达中证金融科技主题交易型开放式指数证券投资基金联接基金</t>
+          <t>易方达周期优选混合型证券投资基金</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>股票型</t>
+          <t>混合型</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -23272,12 +22482,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -23286,19 +22496,15 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>接收材料:2025-09-11; 受理通知:2025-09-16; 一次书面反馈:2026-02-06; 接收书面回复:2026-03-23; 行政许可决定书:2026-03-23</t>
+          <t>接收材料:2025-09-12; 受理通知:2025-09-16; 一次书面反馈:2025-10-29; 接收书面回复:2026-06-03</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证金融科技主题交易型开放式指数证券投资基金联接基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达周期优选混合型证券投资基金》</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -23309,11 +22515,6 @@
       <c r="M159" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
         </is>
       </c>
     </row>
@@ -23325,12 +22526,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>易方达周期优选混合型证券投资基金</t>
+          <t>易方达中证稀土产业交易型开放式指数证券投资基金发起式联接基金</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>混合型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -23340,29 +22541,25 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>接收材料:2025-09-12; 受理通知:2025-09-16; 一次书面反馈:2025-10-29; 接收书面回复:2026-06-03</t>
+          <t>接收材料:2025-09-19</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达周期优选混合型证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证稀土产业交易型开放式指数证券投资基金发起式联接基金》</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -23373,11 +22570,6 @@
       <c r="M160" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
         </is>
       </c>
     </row>
@@ -23389,12 +22581,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>易方达中证稀土产业交易型开放式指数证券投资基金发起式联接基金</t>
+          <t>易方达成长驱动混合型证券投资基金</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>股票型</t>
+          <t>混合型</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -23412,17 +22604,25 @@
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
       <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>接收材料:2025-09-19</t>
+          <t>接收材料:2025-09-19; 受理通知:2025-09-25; 行政许可决定书:2025-11-04</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证稀土产业交易型开放式指数证券投资基金发起式联接基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达成长驱动混合型证券投资基金》</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -23433,11 +22633,6 @@
       <c r="M161" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>2025-09-19</t>
         </is>
       </c>
     </row>
@@ -23449,7 +22644,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>易方达成长驱动混合型证券投资基金</t>
+          <t>易方达科技先锋混合型证券投资基金</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -23464,33 +22659,33 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>接收材料:2025-09-19; 受理通知:2025-09-25; 行政许可决定书:2025-11-04</t>
+          <t>接收材料:2025-09-09; 受理通知:2025-09-16; 行政许可决定书:2025-10-20</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达成长驱动混合型证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达科技先锋混合型证券投资基金》</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -23501,11 +22696,6 @@
       <c r="M162" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>2025-09-19</t>
         </is>
       </c>
     </row>
@@ -23571,11 +22761,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -23639,11 +22824,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -23707,11 +22887,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -23775,11 +22950,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -23843,11 +23013,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -23872,12 +23037,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -23909,11 +23074,6 @@
       <c r="M168" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
         </is>
       </c>
     </row>
@@ -23971,11 +23131,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -24037,11 +23192,6 @@
       <c r="M170" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
         </is>
       </c>
     </row>
@@ -24099,11 +23249,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -24167,11 +23312,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -24235,11 +23375,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -24303,11 +23438,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -24371,11 +23501,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -24400,12 +23525,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -24431,11 +23556,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -24497,11 +23617,6 @@
       <c r="M177" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
         </is>
       </c>
     </row>
@@ -24559,11 +23674,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -24625,11 +23735,6 @@
       <c r="M179" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
         </is>
       </c>
     </row>
@@ -24687,11 +23792,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -24753,11 +23853,6 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
         </is>
       </c>
     </row>
@@ -24817,11 +23912,6 @@
       <c r="M182" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
         </is>
       </c>
     </row>
@@ -24879,11 +23969,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -24943,11 +24028,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -25005,11 +24085,6 @@
       <c r="M185" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
         </is>
       </c>
     </row>
@@ -25067,11 +24142,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -25127,11 +24197,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -25195,11 +24260,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -25261,11 +24321,6 @@
       <c r="M189" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
         </is>
       </c>
     </row>
@@ -25323,11 +24378,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -25391,11 +24441,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -25459,11 +24504,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -25525,11 +24565,6 @@
       <c r="M193" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
         </is>
       </c>
     </row>
@@ -25587,11 +24622,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -25647,11 +24677,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -25713,11 +24738,6 @@
       <c r="M196" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
         </is>
       </c>
     </row>
@@ -25775,11 +24795,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -25804,12 +24819,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
           <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
         </is>
       </c>
       <c r="G198" t="inlineStr"/>
@@ -25835,11 +24850,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -25849,7 +24859,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>易方达中证港股通综合指数量化增强型证券投资基金</t>
+          <t>易方达中证全指红利质量交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -25869,7 +24879,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -25880,17 +24890,17 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>接收材料:2025-12-25; 受理通知:2025-12-30; 行政许可决定书:2026-02-03</t>
+          <t>接收材料:2025-12-26; 受理通知:2025-12-30; 行政许可决定书:2026-01-07</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证港股通综合指数量化增强型证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证全指红利质量交易型开放式指数证券投资基金》</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -25901,11 +24911,6 @@
       <c r="M199" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
         </is>
       </c>
     </row>
@@ -25917,7 +24922,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>易方达中证全指红利质量交易型开放式指数证券投资基金</t>
+          <t>易方达中证港股通综合指数量化增强型证券投资基金</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -25932,7 +24937,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -25948,17 +24953,17 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>接收材料:2025-12-26; 受理通知:2025-12-30; 行政许可决定书:2026-01-07</t>
+          <t>接收材料:2025-12-25; 受理通知:2025-12-30; 行政许可决定书:2026-02-03</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证全指红利质量交易型开放式指数证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达中证港股通综合指数量化增强型证券投资基金》</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -25969,11 +24974,6 @@
       <c r="M200" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
         </is>
       </c>
     </row>
@@ -26031,11 +25031,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -26099,11 +25094,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -26167,11 +25157,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -26235,11 +25220,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -26264,12 +25244,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G205" t="inlineStr"/>
@@ -26295,11 +25275,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -26324,12 +25299,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -26363,11 +25338,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -26431,11 +25401,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -26460,12 +25425,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -26499,11 +25464,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -26528,12 +25488,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -26567,11 +25527,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -26596,12 +25551,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
           <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
         </is>
       </c>
       <c r="G210" t="inlineStr"/>
@@ -26627,11 +25582,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -26656,12 +25606,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
           <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -26693,11 +25643,6 @@
       <c r="M211" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
         </is>
       </c>
     </row>
@@ -26755,11 +25700,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -26821,11 +25761,6 @@
       <c r="M213" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
         </is>
       </c>
     </row>
@@ -26887,11 +25822,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -26955,11 +25885,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -26969,12 +25894,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>易方达恒安稳健6个月持有期债券型证券投资基金</t>
+          <t>易方达上证综合交易型开放式指数证券投资基金联接基金</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>债券型</t>
+          <t>股票型</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26989,20 +25914,28 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr"/>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
       <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>接收材料:2026-02-09</t>
+          <t>接收材料:2026-02-10; 受理通知:2026-02-13; 行政许可决定书:2026-04-10</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达恒安稳健6个月持有期债券型证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达上证综合交易型开放式指数证券投资基金联接基金》</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -27013,11 +25946,6 @@
       <c r="M216" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
         </is>
       </c>
     </row>
@@ -27029,12 +25957,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>易方达上证综合交易型开放式指数证券投资基金联接基金</t>
+          <t>易方达恒安稳健6个月持有期债券型证券投资基金</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>股票型</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -27044,7 +25972,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -27052,25 +25980,17 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>接收材料:2026-02-10; 受理通知:2026-02-13; 行政许可决定书:2026-04-10</t>
+          <t>接收材料:2026-02-09</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达上证综合交易型开放式指数证券投资基金联接基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达恒安稳健6个月持有期债券型证券投资基金》</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -27081,11 +26001,6 @@
       <c r="M217" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
         </is>
       </c>
     </row>
@@ -27151,11 +26066,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -27180,12 +26090,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
           <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -27219,11 +26129,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -27285,11 +26190,6 @@
       <c r="M220" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
         </is>
       </c>
     </row>
@@ -27351,11 +26251,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -27419,11 +26314,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -27433,12 +26323,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>易方达恒安稳健6个月持有期债券型证券投资基金</t>
+          <t>易方达优选盈盛多元配置6个月持有期混合型基金中基金（FOF）</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>债券型</t>
+          <t>基金中基金 (FOF)</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -27453,7 +26343,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -27464,17 +26354,17 @@
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>接收材料:2026-02-27; 受理通知:2026-03-03; 行政许可决定书:2026-03-19</t>
+          <t>接收材料:2026-02-28; 受理通知:2026-03-03; 行政许可决定书:2026-05-08</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达恒安稳健6个月持有期债券型证券投资基金》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达优选盈盛多元配置6个月持有期混合型基金中基金（FOF）》</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -27485,11 +26375,6 @@
       <c r="M223" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
         </is>
       </c>
     </row>
@@ -27501,12 +26386,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>易方达优选盈盛多元配置6个月持有期混合型基金中基金（FOF）</t>
+          <t>易方达恒安稳健6个月持有期债券型证券投资基金</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>基金中基金 (FOF)</t>
+          <t>债券型</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27516,7 +26401,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -27532,17 +26417,17 @@
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>接收材料:2026-02-28; 受理通知:2026-03-03; 行政许可决定书:2026-05-08</t>
+          <t>接收材料:2026-02-27; 受理通知:2026-03-03; 行政许可决定书:2026-03-19</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达优选盈盛多元配置6个月持有期混合型基金中基金（FOF）》</t>
+          <t>关于易方达基金管理有限公司的《公开募集基金募集申请注册-易方达恒安稳健6个月持有期债券型证券投资基金》</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -27553,11 +26438,6 @@
       <c r="M224" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
         </is>
       </c>
     </row>
@@ -27621,11 +26501,6 @@
       <c r="M225" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
         </is>
       </c>
     </row>
@@ -27683,11 +26558,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -27712,12 +26582,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
           <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -27751,11 +26621,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -27819,11 +26684,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -27887,11 +26747,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -27953,11 +26808,6 @@
       <c r="M230" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
         </is>
       </c>
     </row>
@@ -28019,11 +26869,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -28085,11 +26930,6 @@
       <c r="M232" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
         </is>
       </c>
     </row>
@@ -28151,11 +26991,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -28215,11 +27050,6 @@
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -28281,11 +27111,6 @@
       <c r="M235" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
         </is>
       </c>
     </row>
@@ -28345,11 +27170,6 @@
       <c r="M236" t="inlineStr">
         <is>
           <t>中国证监会行政许可网上办理-审批进度公示，按基金公司或产品名称检索。</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
         </is>
       </c>
     </row>
@@ -39436,54 +38256,54 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>广发智选启航混合型证券投资基金</t>
+          <t>广发资源智选股票型发起式证券投资基金</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>广发智选启航混合型证券投资基金</t>
+          <t>广发资源智选股票型发起式证券投资基金</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-05-06 至 2025-05-23</t>
+          <t>2025-08-07 至 2025-08-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.gffunds.com.cn/jjgg/flwj/202504/P020250416328376762074.pdf</t>
+          <t>https://www.gffunds.com.cn/jjgg/flwj/202507/P020250724315005667831.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>广发资源智选股票型发起式证券投资基金</t>
+          <t>广发智选启航混合型证券投资基金</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>广发资源智选股票型发起式证券投资基金</t>
+          <t>广发智选启航混合型证券投资基金</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-08-07 至 2025-08-20</t>
+          <t>2025-05-06 至 2025-05-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.gffunds.com.cn/jjgg/flwj/202507/P020250724315005667831.pdf</t>
+          <t>https://www.gffunds.com.cn/jjgg/flwj/202504/P020250416328376762074.pdf</t>
         </is>
       </c>
     </row>
@@ -40003,61 +38823,61 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>广发上证科创板芯片交易型开放式指数证券投资基金</t>
+          <t>广发上证科创板芯片设计主题交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>广发上证科创板芯片交易型开放式指数证券投资基金</t>
+          <t>广发上证科创板芯片设计主题交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-29 至 2026-01-16</t>
+          <t>2025-11-28 至 2025-12-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.gffunds.com.cn/jjgg/flwj/202512/P020251222352583176234.pdf</t>
+          <t>https://www.gffunds.com.cn/jjgg/flwj/202511/P020251125259173756325.pdf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>广发上证科创板芯片设计主题交易型开放式指数证券投资基金</t>
+          <t>广发上证科创板芯片交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>广发上证科创板芯片设计主题交易型开放式指数证券投资基金</t>
+          <t>广发上证科创板芯片交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-28 至 2025-12-08</t>
+          <t>2025-12-29 至 2026-01-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.gffunds.com.cn/jjgg/flwj/202511/P020251125259173756325.pdf</t>
+          <t>https://www.gffunds.com.cn/jjgg/flwj/202512/P020251222352583176234.pdf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>广发消费领航股票型发起式证券投资基金</t>
+          <t>广发国证新能源电池交易型开放式指数证券投资基金发起式联接基金</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -40067,24 +38887,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>广发消费领航股票型发起式证券投资基金</t>
+          <t>广发国证新能源电池交易型开放式指数证券投资基金发起式联接基金</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-28 至 2026-02-03</t>
+          <t>2026-01-26 至 2026-01-28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.gffunds.com.cn/jjgg/flwj/202601/P020260123324483087941.pdf</t>
+          <t>https://www.gffunds.com.cn/jjgg/flwj/202601/P020260120318786666618.pdf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>广发国证新能源电池交易型开放式指数证券投资基金发起式联接基金</t>
+          <t>广发消费领航股票型发起式证券投资基金</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -40094,17 +38914,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广发国证新能源电池交易型开放式指数证券投资基金发起式联接基金</t>
+          <t>广发消费领航股票型发起式证券投资基金</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-26 至 2026-01-28</t>
+          <t>2026-01-28 至 2026-02-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.gffunds.com.cn/jjgg/flwj/202601/P020260120318786666618.pdf</t>
+          <t>https://www.gffunds.com.cn/jjgg/flwj/202601/P020260123324483087941.pdf</t>
         </is>
       </c>
     </row>
@@ -41812,27 +40632,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>易方达如意盈享6个月持有期混合型发起式基金中基金（FOF）</t>
+          <t>易方达恒生生物科技交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>易方达如意盈享6个月持有期混合型发起式基金中基金（FOF）</t>
+          <t>易方达恒生生物科技交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-12-09 至 2025-12-26</t>
+          <t>2025-09-22 至 2025-10-31</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20251205/%E6%98%93%E6%96%B9%E8%BE%BE%E5%A6%82%E6%84%8F%E7%9B%88%E4%BA%AB6%E4%B8%AA%E6%9C%88%E6%8C%81%E6%9C%89%E6%9C%9F%E6%B7%B7%E5%90%88%E5%9E%8B%E5%8F%91%E8%B5%B7%E5%BC%8F%E5%9F%BA%E9%87%91%E4%B8%AD%E5%9F%BA%E9%87%91%EF%BC%88FOF%EF%BC%89%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
+          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20250919/%E6%98%93%E6%96%B9%E8%BE%BE%E6%81%92%E7%94%9F%E7%94%9F%E7%89%A9%E7%A7%91%E6%8A%80%E4%BA%A4%E6%98%93%E5%9E%8B%E5%BC%80%E6%94%BE%E5%BC%8F%E6%8C%87%E6%95%B0%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
         </is>
       </c>
     </row>
@@ -41849,44 +40669,44 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>易方达恒生生物科技交易型开放式指数证券投资基金</t>
+          <t>易方达恒生生物科技交易型开放式指数证券投资基金发起式联接基金</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-09-22 至 2025-10-31</t>
+          <t>2026-03-09 至 2026-03-20</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20250919/%E6%98%93%E6%96%B9%E8%BE%BE%E6%81%92%E7%94%9F%E7%94%9F%E7%89%A9%E7%A7%91%E6%8A%80%E4%BA%A4%E6%98%93%E5%9E%8B%E5%BC%80%E6%94%BE%E5%BC%8F%E6%8C%87%E6%95%B0%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
+          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20260228/%E6%98%93%E6%96%B9%E8%BE%BE%E6%81%92%E7%94%9F%E7%94%9F%E7%89%A9%E7%A7%91%E6%8A%80%E4%BA%A4%E6%98%93%E5%9E%8B%E5%BC%80%E6%94%BE%E5%BC%8F%E6%8C%87%E6%95%B0%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%8F%91%E8%B5%B7%E5%BC%8F%E8%81%94%E6%8E%A5%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>易方达恒生生物科技交易型开放式指数证券投资基金</t>
+          <t>易方达如意盈享6个月持有期混合型发起式基金中基金（FOF）</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>易方达恒生生物科技交易型开放式指数证券投资基金发起式联接基金</t>
+          <t>易方达如意盈享6个月持有期混合型发起式基金中基金（FOF）</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-09 至 2026-03-20</t>
+          <t>2025-12-09 至 2025-12-26</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20260228/%E6%98%93%E6%96%B9%E8%BE%BE%E6%81%92%E7%94%9F%E7%94%9F%E7%89%A9%E7%A7%91%E6%8A%80%E4%BA%A4%E6%98%93%E5%9E%8B%E5%BC%80%E6%94%BE%E5%BC%8F%E6%8C%87%E6%95%B0%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%8F%91%E8%B5%B7%E5%BC%8F%E8%81%94%E6%8E%A5%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
+          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20251205/%E6%98%93%E6%96%B9%E8%BE%BE%E5%A6%82%E6%84%8F%E7%9B%88%E4%BA%AB6%E4%B8%AA%E6%9C%88%E6%8C%81%E6%9C%89%E6%9C%9F%E6%B7%B7%E5%90%88%E5%9E%8B%E5%8F%91%E8%B5%B7%E5%BC%8F%E5%9F%BA%E9%87%91%E4%B8%AD%E5%9F%BA%E9%87%91%EF%BC%88FOF%EF%BC%89%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
         </is>
       </c>
     </row>
@@ -42217,81 +41037,81 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>易方达科技先锋混合型证券投资基金</t>
+          <t>易方达中证金融科技主题交易型开放式指数证券投资基金联接基金</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>易方达科技先锋混合型证券投资基金</t>
+          <t>易方达中证金融科技主题交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-11-12 至 2025-11-18</t>
+          <t>2025-08-25 至 2025-08-29</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20251104/%E6%98%93%E6%96%B9%E8%BE%BE%E7%A7%91%E6%8A%80%E5%85%88%E9%94%8B%E6%B7%B7%E5%90%88%E5%9E%8B%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
+          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20250821/%E6%98%93%E6%96%B9%E8%BE%BE%E4%B8%AD%E8%AF%81%E9%87%91%E8%9E%8D%E7%A7%91%E6%8A%80%E4%B8%BB%E9%A2%98%E4%BA%A4%E6%98%93%E5%9E%8B%E5%BC%80%E6%94%BE%E5%BC%8F%E6%8C%87%E6%95%B0%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>易方达中证金融科技主题交易型开放式指数证券投资基金联接基金</t>
+          <t>易方达成长驱动混合型证券投资基金</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>易方达中证金融科技主题交易型开放式指数证券投资基金</t>
+          <t>易方达成长驱动混合型证券投资基金</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-08-25 至 2025-08-29</t>
+          <t>2026-01-28 至 2026-02-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20250821/%E6%98%93%E6%96%B9%E8%BE%BE%E4%B8%AD%E8%AF%81%E9%87%91%E8%9E%8D%E7%A7%91%E6%8A%80%E4%B8%BB%E9%A2%98%E4%BA%A4%E6%98%93%E5%9E%8B%E5%BC%80%E6%94%BE%E5%BC%8F%E6%8C%87%E6%95%B0%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
+          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20260121/%E6%98%93%E6%96%B9%E8%BE%BE%E6%88%90%E9%95%BF%E9%A9%B1%E5%8A%A8%E6%B7%B7%E5%90%88%E5%9E%8B%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>易方达成长驱动混合型证券投资基金</t>
+          <t>易方达科技先锋混合型证券投资基金</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>易方达成长驱动混合型证券投资基金</t>
+          <t>易方达科技先锋混合型证券投资基金</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-01-28 至 2026-02-10</t>
+          <t>2025-11-12 至 2025-11-18</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20260121/%E6%98%93%E6%96%B9%E8%BE%BE%E6%88%90%E9%95%BF%E9%A9%B1%E5%8A%A8%E6%B7%B7%E5%90%88%E5%9E%8B%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
+          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20251104/%E6%98%93%E6%96%B9%E8%BE%BE%E7%A7%91%E6%8A%80%E5%85%88%E9%94%8B%E6%B7%B7%E5%90%88%E5%9E%8B%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
         </is>
       </c>
     </row>
@@ -43027,7 +41847,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>易方达中证港股通综合指数量化增强型证券投资基金</t>
+          <t>易方达中证全指红利质量交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -43037,24 +41857,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>易方达中证港股通综合指数量化增强型证券投资基金</t>
+          <t>易方达中证全指红利质量交易型开放式指数证券投资基金</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-03-04 至 2026-03-17</t>
+          <t>2026-02-02 至 2026-02-06</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20260228/%E6%98%93%E6%96%B9%E8%BE%BE%E4%B8%AD%E8%AF%81%E6%B8%AF%E8%82%A1%E9%80%9A%E7%BB%BC%E5%90%88%E6%8C%87%E6%95%B0%E9%87%8F%E5%8C%96%E5%A2%9E%E5%BC%BA%E5%9E%8B%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
+          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20260127/%E6%98%93%E6%96%B9%E8%BE%BE%E4%B8%AD%E8%AF%81%E5%85%A8%E6%8C%87%E7%BA%A2%E5%88%A9%E8%B4%A8%E9%87%8F%E4%BA%A4%E6%98%93%E5%9E%8B%E5%BC%80%E6%94%BE%E5%BC%8F%E6%8C%87%E6%95%B0%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>易方达中证全指红利质量交易型开放式指数证券投资基金</t>
+          <t>易方达中证港股通综合指数量化增强型证券投资基金</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -43064,17 +41884,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>易方达中证全指红利质量交易型开放式指数证券投资基金</t>
+          <t>易方达中证港股通综合指数量化增强型证券投资基金</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-02-02 至 2026-02-06</t>
+          <t>2026-03-04 至 2026-03-17</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20260127/%E6%98%93%E6%96%B9%E8%BE%BE%E4%B8%AD%E8%AF%81%E5%85%A8%E6%8C%87%E7%BA%A2%E5%88%A9%E8%B4%A8%E9%87%8F%E4%BA%A4%E6%98%93%E5%9E%8B%E5%BC%80%E6%94%BE%E5%BC%8F%E6%8C%87%E6%95%B0%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
+          <t>https://cdn.efunds.com.cn/owch/data/bulletin/20260228/%E6%98%93%E6%96%B9%E8%BE%BE%E4%B8%AD%E8%AF%81%E6%B8%AF%E8%82%A1%E9%80%9A%E7%BB%BC%E5%90%88%E6%8C%87%E6%95%B0%E9%87%8F%E5%8C%96%E5%A2%9E%E5%BC%BA%E5%9E%8B%E8%AF%81%E5%88%B8%E6%8A%95%E8%B5%84%E5%9F%BA%E9%87%91%E5%9F%BA%E9%87%91%E4%BB%BD%E9%A2%9D%E5%8F%91%E5%94%AE%E5%85%AC%E5%91%8A.pdf</t>
         </is>
       </c>
     </row>
